--- a/Results/Somatostatin Proportions/Somatostatin_Content_AO_Analysis.xlsx
+++ b/Results/Somatostatin Proportions/Somatostatin_Content_AO_Analysis.xlsx
@@ -1519,19 +1519,19 @@
         <v>111</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0414</v>
+        <v>-0.0062</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0165</v>
+        <v>-0.0222</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0659</v>
+        <v>0.011</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.2158</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.7842</v>
       </c>
     </row>
     <row r="7">
@@ -1539,19 +1539,19 @@
         <v>112</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0598</v>
+        <v>0.006</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0241</v>
+        <v>-0.0586</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1503</v>
+        <v>0.0697</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9185</v>
+        <v>0.5755</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0815</v>
+        <v>0.4245</v>
       </c>
     </row>
     <row r="8">
@@ -1559,19 +1559,19 @@
         <v>113</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0512</v>
+        <v>-0.0059</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0773</v>
+        <v>-0.0216</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0287</v>
+        <v>0.0095</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.2255</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.7745</v>
       </c>
     </row>
     <row r="9">
@@ -1579,19 +1579,19 @@
         <v>114</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0096</v>
+        <v>-0.012</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0346</v>
+        <v>-0.0294</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0157</v>
+        <v>0.004</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2075</v>
+        <v>0.0608</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7925</v>
+        <v>0.9392</v>
       </c>
     </row>
     <row r="10">
@@ -1599,19 +1599,19 @@
         <v>115</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0257</v>
+        <v>0.0156</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1158</v>
+        <v>-0.054</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0626</v>
+        <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>0.287</v>
+        <v>0.6828</v>
       </c>
       <c r="F10" t="n">
-        <v>0.713</v>
+        <v>0.3172</v>
       </c>
     </row>
     <row r="11">
@@ -1619,19 +1619,19 @@
         <v>116</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0095</v>
+        <v>0.0003</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0847</v>
+        <v>-0.0641</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1029</v>
+        <v>0.0631</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5838</v>
+        <v>0.505</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4162</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="12">
@@ -1639,19 +1639,19 @@
         <v>117</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0246</v>
+        <v>-0.0213</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1032</v>
+        <v>-0.0896</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0613</v>
+        <v>0.044</v>
       </c>
       <c r="E12" t="n">
-        <v>0.264</v>
+        <v>0.254</v>
       </c>
       <c r="F12" t="n">
-        <v>0.736</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="13">
@@ -1659,19 +1659,19 @@
         <v>118</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0169</v>
+        <v>-0.0274</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0683</v>
+        <v>-0.0972</v>
       </c>
       <c r="D13" t="n">
-        <v>0.106</v>
+        <v>0.0351</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6388</v>
+        <v>0.1868</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3612</v>
+        <v>0.8132</v>
       </c>
     </row>
     <row r="14">
@@ -1679,19 +1679,19 @@
         <v>119</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0355</v>
+        <v>-0.0151</v>
       </c>
       <c r="C14" t="n">
-        <v>0.011</v>
+        <v>-0.0334</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0599</v>
+        <v>0.0024</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9975</v>
+        <v>0.043</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0025</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="15">
@@ -1699,19 +1699,19 @@
         <v>120</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0191</v>
+        <v>-0.0122</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1137</v>
+        <v>-0.0818</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0688</v>
+        <v>0.0442</v>
       </c>
       <c r="E15" t="n">
-        <v>0.341</v>
+        <v>0.339</v>
       </c>
       <c r="F15" t="n">
-        <v>0.659</v>
+        <v>0.661</v>
       </c>
     </row>
     <row r="16">
@@ -1719,19 +1719,19 @@
         <v>121</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0542</v>
+        <v>-0.0054</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1452</v>
+        <v>-0.0709</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0276</v>
+        <v>0.0568</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1042</v>
+        <v>0.4275</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8958</v>
+        <v>0.5725</v>
       </c>
     </row>
     <row r="17">
@@ -1739,19 +1739,19 @@
         <v>122</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.0123</v>
+        <v>-0.012</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1063</v>
+        <v>-0.0759</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0791</v>
+        <v>0.0518</v>
       </c>
       <c r="E17" t="n">
-        <v>0.389</v>
+        <v>0.3435</v>
       </c>
       <c r="F17" t="n">
-        <v>0.611</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="18">
@@ -1759,19 +1759,19 @@
         <v>123</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.0034</v>
+        <v>0.0003</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0973</v>
+        <v>-0.0648</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0874</v>
+        <v>0.0627</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4695</v>
+        <v>0.5032</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5305</v>
+        <v>0.4968</v>
       </c>
     </row>
     <row r="19">
@@ -1779,19 +1779,19 @@
         <v>124</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.029</v>
+        <v>0.0156</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0531</v>
+        <v>-0.0018</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0084</v>
+        <v>0.0335</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0035</v>
+        <v>0.9635</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9965</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="20">
@@ -1799,19 +1799,19 @@
         <v>125</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0063</v>
+        <v>0.0003</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0156</v>
+        <v>-0.0162</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0304</v>
+        <v>0.0157</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6972</v>
+        <v>0.5152</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3028</v>
+        <v>0.4848</v>
       </c>
     </row>
   </sheetData>
@@ -1854,13 +1854,13 @@
         <v>49</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1634</v>
+        <v>0.1528</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1256</v>
+        <v>0.1195</v>
       </c>
       <c r="D4" t="n">
-        <v>0.207</v>
+        <v>0.1889</v>
       </c>
     </row>
     <row r="5">
@@ -1868,13 +1868,13 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2025</v>
+        <v>0.1417</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1602</v>
+        <v>0.111</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2543</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="6">
@@ -1882,13 +1882,13 @@
         <v>51</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2043</v>
+        <v>0.148</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1594</v>
+        <v>0.1148</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2532</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="7">
@@ -1926,19 +1926,19 @@
         <v>58</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0387</v>
+        <v>0.0107</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0598</v>
+        <v>-0.0012</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0199</v>
+        <v>0.0233</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0003</v>
+        <v>0.9655</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9998</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="11">
@@ -1946,19 +1946,19 @@
         <v>59</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0405</v>
+        <v>0.0048</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0589</v>
+        <v>-0.0061</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0221</v>
+        <v>0.0172</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.797</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="12">
@@ -1966,19 +1966,19 @@
         <v>60</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0016</v>
+        <v>-0.0059</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0204</v>
+        <v>-0.0172</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0188</v>
+        <v>0.0063</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4377</v>
+        <v>0.1532</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5622</v>
+        <v>0.8468</v>
       </c>
     </row>
   </sheetData>
@@ -2021,13 +2021,13 @@
         <v>63</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1816</v>
+        <v>0.1415</v>
       </c>
       <c r="C4" t="n">
-        <v>0.125</v>
+        <v>0.1039</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2439</v>
+        <v>0.1831</v>
       </c>
     </row>
     <row r="5">
@@ -2035,13 +2035,13 @@
         <v>64</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1977</v>
+        <v>0.1528</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1364</v>
+        <v>0.1023</v>
       </c>
       <c r="D5" t="n">
-        <v>0.262</v>
+        <v>0.2037</v>
       </c>
     </row>
     <row r="6">
@@ -2079,19 +2079,19 @@
         <v>66</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0155</v>
+        <v>-0.0109</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1008</v>
+        <v>-0.0776</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0724</v>
+        <v>0.0476</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3575</v>
+        <v>0.3572</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6425</v>
+        <v>0.6428</v>
       </c>
     </row>
   </sheetData>
@@ -2140,13 +2140,13 @@
         <v>63</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1503</v>
+        <v>0.1416</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0998</v>
+        <v>0.099</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2088</v>
+        <v>0.1814</v>
       </c>
     </row>
     <row r="5">
@@ -2157,13 +2157,13 @@
         <v>64</v>
       </c>
       <c r="C5" t="n">
-        <v>0.176</v>
+        <v>0.1635</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1177</v>
+        <v>0.111</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2366</v>
+        <v>0.2177</v>
       </c>
     </row>
     <row r="6">
@@ -2174,13 +2174,13 @@
         <v>63</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1925</v>
+        <v>0.1352</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1309</v>
+        <v>0.0986</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2572</v>
+        <v>0.1782</v>
       </c>
     </row>
     <row r="7">
@@ -2191,13 +2191,13 @@
         <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2113</v>
+        <v>0.1477</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1495</v>
+        <v>0.1007</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2839</v>
+        <v>0.2009</v>
       </c>
     </row>
     <row r="8">
@@ -2208,13 +2208,13 @@
         <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2021</v>
+        <v>0.1474</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1419</v>
+        <v>0.1056</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2703</v>
+        <v>0.1891</v>
       </c>
     </row>
     <row r="9">
@@ -2225,13 +2225,13 @@
         <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2061</v>
+        <v>0.1474</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1395</v>
+        <v>0.0978</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2729</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="10">
@@ -2275,19 +2275,19 @@
         <v>49</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0246</v>
+        <v>-0.0213</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1032</v>
+        <v>-0.0896</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0613</v>
+        <v>0.044</v>
       </c>
       <c r="F13" t="n">
-        <v>0.264</v>
+        <v>0.254</v>
       </c>
       <c r="G13" t="n">
-        <v>0.736</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="14">
@@ -2298,19 +2298,19 @@
         <v>50</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0191</v>
+        <v>-0.0122</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1137</v>
+        <v>-0.0818</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0688</v>
+        <v>0.0442</v>
       </c>
       <c r="F14" t="n">
-        <v>0.341</v>
+        <v>0.339</v>
       </c>
       <c r="G14" t="n">
-        <v>0.659</v>
+        <v>0.661</v>
       </c>
     </row>
     <row r="15">
@@ -2321,19 +2321,19 @@
         <v>51</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0034</v>
+        <v>0.0003</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0973</v>
+        <v>-0.0648</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0874</v>
+        <v>0.0627</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4695</v>
+        <v>0.5032</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5305</v>
+        <v>0.4968</v>
       </c>
     </row>
     <row r="16">
@@ -2377,19 +2377,19 @@
         <v>63</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0414</v>
+        <v>0.0062</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0659</v>
+        <v>-0.011</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0165</v>
+        <v>0.0222</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.7842</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0.2158</v>
       </c>
     </row>
     <row r="20">
@@ -2400,19 +2400,19 @@
         <v>63</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0512</v>
+        <v>-0.0059</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0773</v>
+        <v>-0.0216</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0287</v>
+        <v>0.0095</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.2255</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0.7745</v>
       </c>
     </row>
     <row r="21">
@@ -2423,19 +2423,19 @@
         <v>63</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0096</v>
+        <v>-0.012</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0346</v>
+        <v>-0.0294</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0157</v>
+        <v>0.004</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2075</v>
+        <v>0.0608</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7925</v>
+        <v>0.9392</v>
       </c>
     </row>
     <row r="22">
@@ -2446,19 +2446,19 @@
         <v>64</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0355</v>
+        <v>0.0151</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0599</v>
+        <v>-0.0024</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.011</v>
+        <v>0.0334</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0025</v>
+        <v>0.957</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9975</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="23">
@@ -2469,19 +2469,19 @@
         <v>64</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.029</v>
+        <v>0.0156</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0531</v>
+        <v>-0.0018</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0084</v>
+        <v>0.0335</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0035</v>
+        <v>0.9635</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9965</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="24">
@@ -2492,19 +2492,19 @@
         <v>64</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0063</v>
+        <v>0.0003</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0156</v>
+        <v>-0.0162</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0304</v>
+        <v>0.0157</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6972</v>
+        <v>0.5152</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3028</v>
+        <v>0.4848</v>
       </c>
     </row>
   </sheetData>
@@ -2558,19 +2558,19 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0119</v>
+        <v>-0.0061</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0215</v>
+        <v>-0.0124</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0029</v>
+        <v>0.0002</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001</v>
+        <v>0.0198</v>
       </c>
       <c r="F5" t="n">
-        <v>0.999</v>
+        <v>0.9802</v>
       </c>
     </row>
     <row r="6">
@@ -2608,19 +2608,19 @@
         <v>49</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0128</v>
+        <v>-0.0077</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0223</v>
+        <v>-0.0147</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0044</v>
+        <v>-0.0016</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0005</v>
+        <v>0.0065</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9995</v>
+        <v>0.9935</v>
       </c>
     </row>
     <row r="10">
@@ -2628,19 +2628,19 @@
         <v>50</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.013</v>
+        <v>-0.0063</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0227</v>
+        <v>-0.0129</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.003</v>
+        <v>-0.0003</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0013</v>
+        <v>0.0177</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9988</v>
+        <v>0.9822</v>
       </c>
     </row>
     <row r="11">
@@ -2648,19 +2648,19 @@
         <v>51</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0099</v>
+        <v>-0.0044</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.02</v>
+        <v>-0.0106</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0006</v>
+        <v>0.0021</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0105</v>
+        <v>0.0782</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9895</v>
+        <v>0.9218</v>
       </c>
     </row>
     <row r="12">
@@ -2698,19 +2698,19 @@
         <v>58</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>-0.0015</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0045</v>
+        <v>-0.0041</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0045</v>
+        <v>0.001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.506</v>
+        <v>0.1272</v>
       </c>
       <c r="F15" t="n">
-        <v>0.494</v>
+        <v>0.8728</v>
       </c>
     </row>
     <row r="16">
@@ -2718,19 +2718,19 @@
         <v>59</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.003</v>
+        <v>-0.0034</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0069</v>
+        <v>-0.0059</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0013</v>
+        <v>-0.0008</v>
       </c>
       <c r="E16" t="n">
-        <v>0.088</v>
+        <v>0.0035</v>
       </c>
       <c r="F16" t="n">
-        <v>0.912</v>
+        <v>0.9965</v>
       </c>
     </row>
     <row r="17">
@@ -2738,19 +2738,19 @@
         <v>60</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.003</v>
+        <v>-0.0019</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0076</v>
+        <v>-0.0046</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0017</v>
+        <v>0.0004</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1088</v>
+        <v>0.0635</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8912</v>
+        <v>0.9365</v>
       </c>
     </row>
     <row r="18">
@@ -2788,19 +2788,19 @@
         <v>63</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.0099</v>
+        <v>-0.0046</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0213</v>
+        <v>-0.0126</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0008</v>
+        <v>0.0032</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0278</v>
+        <v>0.121</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9722</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="22">
@@ -2808,19 +2808,19 @@
         <v>64</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.0138</v>
+        <v>-0.0076</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0269</v>
+        <v>-0.0174</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0017</v>
+        <v>0.0018</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0065</v>
+        <v>0.0382</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9935</v>
+        <v>0.9618</v>
       </c>
     </row>
     <row r="23">
@@ -2858,19 +2858,19 @@
         <v>66</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0042</v>
+        <v>0.0033</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0116</v>
+        <v>-0.0081</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0205</v>
+        <v>0.0167</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7022</v>
+        <v>0.7078</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2978</v>
+        <v>0.2922</v>
       </c>
     </row>
   </sheetData>
@@ -2924,19 +2924,19 @@
         <v>24</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0037</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0085</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0019</v>
+        <v>0.0003</v>
       </c>
       <c r="E5" t="n">
-        <v>0.095</v>
+        <v>0.0345</v>
       </c>
       <c r="F5" t="n">
-        <v>0.905</v>
+        <v>0.9655</v>
       </c>
     </row>
     <row r="6">
@@ -2974,19 +2974,19 @@
         <v>49</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0061</v>
+        <v>-0.0056</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0118</v>
+        <v>-0.0106</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0006</v>
+        <v>-0.001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0112</v>
+        <v>0.0055</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9888</v>
+        <v>0.9945</v>
       </c>
     </row>
     <row r="10">
@@ -2994,19 +2994,19 @@
         <v>50</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0096</v>
+        <v>-0.0085</v>
       </c>
       <c r="D10" t="n">
-        <v>0.003</v>
+        <v>0.0006</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1348</v>
+        <v>0.0398</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8652</v>
+        <v>0.9602</v>
       </c>
     </row>
     <row r="11">
@@ -3014,19 +3014,19 @@
         <v>51</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0015</v>
+        <v>-0.0018</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0077</v>
+        <v>-0.0065</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0045</v>
+        <v>0.0022</v>
       </c>
       <c r="E11" t="n">
-        <v>0.305</v>
+        <v>0.2008</v>
       </c>
       <c r="F11" t="n">
-        <v>0.695</v>
+        <v>0.7992</v>
       </c>
     </row>
     <row r="12">
@@ -3064,19 +3064,19 @@
         <v>58</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0029</v>
+        <v>-0.002</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0051</v>
+        <v>-0.0037</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.001</v>
+        <v>-0.0004</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0027</v>
+        <v>0.0063</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9972</v>
+        <v>0.9938</v>
       </c>
     </row>
     <row r="16">
@@ -3084,13 +3084,13 @@
         <v>59</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0046</v>
+        <v>-0.0039</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0066</v>
+        <v>-0.0055</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0025</v>
+        <v>-0.0023</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3104,19 +3104,19 @@
         <v>60</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.0018</v>
+        <v>-0.0019</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0036</v>
+        <v>-0.0035</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0001</v>
+        <v>-0.0004</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0302</v>
+        <v>0.0065</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9698</v>
+        <v>0.9935</v>
       </c>
     </row>
     <row r="18">
@@ -3154,19 +3154,19 @@
         <v>63</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.0023</v>
+        <v>-0.0025</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0067</v>
+        <v>-0.0065</v>
       </c>
       <c r="D21" t="n">
-        <v>0.003</v>
+        <v>0.0017</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1912</v>
+        <v>0.1265</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8088</v>
+        <v>0.8735</v>
       </c>
     </row>
     <row r="22">
@@ -3174,19 +3174,19 @@
         <v>64</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.0051</v>
+        <v>-0.0049</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0162</v>
+        <v>-0.0132</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0042</v>
+        <v>0.0031</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1375</v>
+        <v>0.093</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8625</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="23">
@@ -3224,19 +3224,19 @@
         <v>66</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0031</v>
+        <v>0.0026</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0071</v>
+        <v>-0.0065</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0141</v>
+        <v>0.0119</v>
       </c>
       <c r="E26" t="n">
-        <v>0.718</v>
+        <v>0.7145</v>
       </c>
       <c r="F26" t="n">
-        <v>0.282</v>
+        <v>0.2855</v>
       </c>
     </row>
   </sheetData>
@@ -3290,13 +3290,13 @@
         <v>25</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0188</v>
+        <v>-0.0118</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0224</v>
+        <v>-0.0142</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0153</v>
+        <v>-0.0094</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3340,19 +3340,19 @@
         <v>49</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0022</v>
+        <v>0.003</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0057</v>
+        <v>0.0004</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0007</v>
+        <v>0.0057</v>
       </c>
       <c r="E9" t="n">
-        <v>0.074</v>
+        <v>0.9885</v>
       </c>
       <c r="F9" t="n">
-        <v>0.926</v>
+        <v>0.0115</v>
       </c>
     </row>
     <row r="10">
@@ -3360,13 +3360,13 @@
         <v>50</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0278</v>
+        <v>-0.0198</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.034</v>
+        <v>-0.0247</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0212</v>
+        <v>-0.0158</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3380,13 +3380,13 @@
         <v>51</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0261</v>
+        <v>-0.0186</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0313</v>
+        <v>-0.022</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0204</v>
+        <v>-0.0146</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3430,13 +3430,13 @@
         <v>58</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0257</v>
+        <v>0.0228</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0191</v>
+        <v>0.0175</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0327</v>
+        <v>0.0283</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -3450,13 +3450,13 @@
         <v>59</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0238</v>
+        <v>0.0216</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0178</v>
+        <v>0.0164</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0296</v>
+        <v>0.0263</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -3470,19 +3470,19 @@
         <v>60</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.0017</v>
+        <v>-0.0012</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0086</v>
+        <v>-0.0055</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0045</v>
+        <v>0.0027</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3028</v>
+        <v>0.2652</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6972</v>
+        <v>0.7348</v>
       </c>
     </row>
     <row r="18">
@@ -3520,13 +3520,13 @@
         <v>63</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.0181</v>
+        <v>-0.0113</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0231</v>
+        <v>-0.0147</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0133</v>
+        <v>-0.0084</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -3540,13 +3540,13 @@
         <v>64</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.0194</v>
+        <v>-0.0121</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0246</v>
+        <v>-0.0161</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0146</v>
+        <v>-0.0086</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -3590,19 +3590,19 @@
         <v>66</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0014</v>
+        <v>0.0009</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0055</v>
+        <v>-0.0041</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0081</v>
+        <v>0.0056</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6552</v>
+        <v>0.6342</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3448</v>
+        <v>0.3658</v>
       </c>
     </row>
   </sheetData>
@@ -3677,19 +3677,19 @@
         <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.013</v>
+        <v>-0.0078</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0226</v>
+        <v>-0.0148</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0049</v>
+        <v>-0.0015</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0003</v>
+        <v>0.0065</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9998</v>
+        <v>0.9935</v>
       </c>
     </row>
     <row r="9">
@@ -3700,19 +3700,19 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0124</v>
+        <v>-0.0058</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0224</v>
+        <v>-0.0122</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0034</v>
+        <v>0.0004</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001</v>
+        <v>0.0238</v>
       </c>
       <c r="G9" t="n">
-        <v>0.999</v>
+        <v>0.9762</v>
       </c>
     </row>
     <row r="10">
@@ -3723,19 +3723,19 @@
         <v>96</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0095</v>
+        <v>-0.0041</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0191</v>
+        <v>-0.0103</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0005</v>
+        <v>0.0024</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0095</v>
+        <v>0.09</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9905</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="11">
@@ -3746,19 +3746,19 @@
         <v>97</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0126</v>
+        <v>-0.0076</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.022</v>
+        <v>-0.0143</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0038</v>
+        <v>-0.0011</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0005</v>
+        <v>0.0073</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9995</v>
+        <v>0.9928</v>
       </c>
     </row>
     <row r="12">
@@ -3769,19 +3769,19 @@
         <v>97</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0135</v>
+        <v>-0.0067</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0241</v>
+        <v>-0.0134</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0035</v>
+        <v>-0.0007</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0013</v>
+        <v>0.0125</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9988</v>
+        <v>0.9875</v>
       </c>
     </row>
     <row r="13">
@@ -3792,19 +3792,19 @@
         <v>97</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0103</v>
+        <v>-0.0047</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0209</v>
+        <v>-0.0114</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0006</v>
+        <v>0.0017</v>
       </c>
       <c r="F13" t="n">
-        <v>0.012</v>
+        <v>0.0703</v>
       </c>
       <c r="G13" t="n">
-        <v>0.988</v>
+        <v>0.9298</v>
       </c>
     </row>
     <row r="14">
@@ -3848,19 +3848,19 @@
         <v>99</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0004</v>
+        <v>0.0001</v>
       </c>
       <c r="D17" t="n">
         <v>-0.0013</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0021</v>
+        <v>0.0016</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6675</v>
+        <v>0.5792</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3325</v>
+        <v>0.4208</v>
       </c>
     </row>
     <row r="18">
@@ -3871,19 +3871,19 @@
         <v>99</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0011</v>
+        <v>-0.0009</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.003</v>
+        <v>-0.0021</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0008</v>
+        <v>0.0005</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1042</v>
+        <v>0.1005</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8958</v>
+        <v>0.8995</v>
       </c>
     </row>
     <row r="19">
@@ -3894,19 +3894,19 @@
         <v>99</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0009</v>
+        <v>-0.0007</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0027</v>
+        <v>-0.002</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001</v>
+        <v>0.0007</v>
       </c>
       <c r="F19" t="n">
-        <v>0.169</v>
+        <v>0.1625</v>
       </c>
       <c r="G19" t="n">
-        <v>0.831</v>
+        <v>0.8375</v>
       </c>
     </row>
   </sheetData>
@@ -3981,19 +3981,19 @@
         <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0152</v>
+        <v>-0.0098</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0253</v>
+        <v>-0.0168</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0066</v>
+        <v>-0.0034</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.9995</v>
       </c>
     </row>
     <row r="9">
@@ -4004,19 +4004,19 @@
         <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0156</v>
+        <v>-0.0082</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0259</v>
+        <v>-0.0154</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0042</v>
+        <v>-0.0014</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.9945</v>
       </c>
     </row>
     <row r="10">
@@ -4027,19 +4027,19 @@
         <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0123</v>
+        <v>-0.0061</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0231</v>
+        <v>-0.0131</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0019</v>
+        <v>0.0011</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0045</v>
+        <v>0.0367</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9955</v>
+        <v>0.9633</v>
       </c>
     </row>
     <row r="11">
@@ -4050,19 +4050,19 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0105</v>
+        <v>-0.0057</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0196</v>
+        <v>-0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0025</v>
+        <v>0.0006</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0025</v>
+        <v>0.0372</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9975</v>
+        <v>0.9628</v>
       </c>
     </row>
     <row r="12">
@@ -4073,19 +4073,19 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0106</v>
+        <v>-0.0047</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0198</v>
+        <v>-0.011</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0019</v>
+        <v>0.0004</v>
       </c>
       <c r="F12" t="n">
-        <v>0.004</v>
+        <v>0.041</v>
       </c>
       <c r="G12" t="n">
-        <v>0.996</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="13">
@@ -4096,19 +4096,19 @@
         <v>106</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0077</v>
+        <v>-0.0029</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0169</v>
+        <v>-0.0087</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0007</v>
+        <v>0.0029</v>
       </c>
       <c r="F13" t="n">
-        <v>0.029</v>
+        <v>0.159</v>
       </c>
       <c r="G13" t="n">
-        <v>0.971</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="14">
@@ -4152,13 +4152,13 @@
         <v>108</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0047</v>
+        <v>0.0041</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0032</v>
+        <v>0.0029</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0063</v>
+        <v>0.0054</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -4175,13 +4175,13 @@
         <v>108</v>
       </c>
       <c r="C18" t="n">
-        <v>0.005</v>
+        <v>0.0034</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0026</v>
+        <v>0.0018</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0076</v>
+        <v>0.0053</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -4198,13 +4198,13 @@
         <v>108</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0046</v>
+        <v>0.0032</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0024</v>
+        <v>0.0016</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0069</v>
+        <v>0.0048</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
